--- a/myapp/files/80_distances/distances_pValue_Risks.xlsx
+++ b/myapp/files/80_distances/distances_pValue_Risks.xlsx
@@ -422,10 +422,10 @@
         <v>9</v>
       </c>
       <c r="E2" t="n">
-        <v>6.7159</v>
+        <v>0.3368</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0004</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -442,10 +442,10 @@
         <v>9</v>
       </c>
       <c r="E3" t="n">
-        <v>5.1484</v>
+        <v>0.2867</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0024</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -462,7 +462,7 @@
         <v>11</v>
       </c>
       <c r="E4" t="n">
-        <v>10.684</v>
+        <v>0.3867</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -482,10 +482,10 @@
         <v>11</v>
       </c>
       <c r="E5" t="n">
-        <v>3.4867</v>
+        <v>0.3067</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0151</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="6">
@@ -502,10 +502,10 @@
         <v>12</v>
       </c>
       <c r="E6" t="n">
-        <v>5.1324</v>
+        <v>0.24</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0023</v>
+        <v>0.0043</v>
       </c>
     </row>
     <row r="7">
@@ -522,10 +522,10 @@
         <v>12</v>
       </c>
       <c r="E7" t="n">
-        <v>1.6578</v>
+        <v>0.1067</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1413</v>
+        <v>0.346</v>
       </c>
     </row>
     <row r="8">
@@ -542,10 +542,10 @@
         <v>13</v>
       </c>
       <c r="E8" t="n">
-        <v>4.0583</v>
+        <v>0.179</v>
       </c>
       <c r="F8" t="n">
-        <v>0.008</v>
+        <v>0.0752</v>
       </c>
     </row>
     <row r="9">
@@ -562,10 +562,10 @@
         <v>13</v>
       </c>
       <c r="E9" t="n">
-        <v>1.5668</v>
+        <v>0.1157</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1601</v>
+        <v>0.1827</v>
       </c>
     </row>
     <row r="10">
@@ -582,10 +582,10 @@
         <v>14</v>
       </c>
       <c r="E10" t="n">
-        <v>7.6349</v>
+        <v>0.3833</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -602,10 +602,10 @@
         <v>14</v>
       </c>
       <c r="E11" t="n">
-        <v>4.9671</v>
+        <v>0.2707</v>
       </c>
       <c r="F11" t="n">
-        <v>0.003</v>
+        <v>0.0001</v>
       </c>
     </row>
     <row r="12">
@@ -621,8 +621,8 @@
       <c r="D12" t="s">
         <v>15</v>
       </c>
-      <c r="E12" t="e">
-        <v>#NUM!</v>
+      <c r="E12" t="n">
+        <v>0.8927</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -641,8 +641,8 @@
       <c r="D13" t="s">
         <v>15</v>
       </c>
-      <c r="E13" t="e">
-        <v>#NUM!</v>
+      <c r="E13" t="n">
+        <v>0.9194</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -662,10 +662,10 @@
         <v>11</v>
       </c>
       <c r="E14" t="n">
-        <v>1.4509</v>
+        <v>0.1094</v>
       </c>
       <c r="F14" t="n">
-        <v>0.1887</v>
+        <v>0.3357</v>
       </c>
     </row>
     <row r="15">
@@ -682,10 +682,10 @@
         <v>11</v>
       </c>
       <c r="E15" t="n">
-        <v>0.2874</v>
+        <v>0.0596</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9467</v>
+        <v>0.9559</v>
       </c>
     </row>
     <row r="16">
@@ -702,10 +702,10 @@
         <v>12</v>
       </c>
       <c r="E16" t="n">
-        <v>5.5095</v>
+        <v>0.2489</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0016</v>
+        <v>0.0002</v>
       </c>
     </row>
     <row r="17">
@@ -722,10 +722,10 @@
         <v>12</v>
       </c>
       <c r="E17" t="n">
-        <v>2.8706</v>
+        <v>0.18</v>
       </c>
       <c r="F17" t="n">
-        <v>0.0321</v>
+        <v>0.0167</v>
       </c>
     </row>
     <row r="18">
@@ -742,10 +742,10 @@
         <v>13</v>
       </c>
       <c r="E18" t="n">
-        <v>7.2684</v>
+        <v>0.188</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -762,10 +762,10 @@
         <v>13</v>
       </c>
       <c r="E19" t="n">
-        <v>4.162</v>
+        <v>0.1709</v>
       </c>
       <c r="F19" t="n">
-        <v>0.0073</v>
+        <v>0.0014</v>
       </c>
     </row>
     <row r="20">
@@ -782,10 +782,10 @@
         <v>14</v>
       </c>
       <c r="E20" t="n">
-        <v>17.309</v>
+        <v>0.0588</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>0.0043</v>
       </c>
     </row>
     <row r="21">
@@ -802,10 +802,10 @@
         <v>14</v>
       </c>
       <c r="E21" t="n">
-        <v>1.5323</v>
+        <v>0.0239</v>
       </c>
       <c r="F21" t="n">
-        <v>0.1689</v>
+        <v>0.7303</v>
       </c>
     </row>
     <row r="22">
@@ -821,8 +821,8 @@
       <c r="D22" t="s">
         <v>15</v>
       </c>
-      <c r="E22" t="e">
-        <v>#NUM!</v>
+      <c r="E22" t="n">
+        <v>0.5559</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
@@ -841,8 +841,8 @@
       <c r="D23" t="s">
         <v>15</v>
       </c>
-      <c r="E23" t="e">
-        <v>#NUM!</v>
+      <c r="E23" t="n">
+        <v>0.7321</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -862,10 +862,10 @@
         <v>12</v>
       </c>
       <c r="E24" t="n">
-        <v>3.9792</v>
+        <v>0.3067</v>
       </c>
       <c r="F24" t="n">
-        <v>0.0086</v>
+        <v>0.0011</v>
       </c>
     </row>
     <row r="25">
@@ -882,10 +882,10 @@
         <v>12</v>
       </c>
       <c r="E25" t="n">
-        <v>2.8681</v>
+        <v>0.2</v>
       </c>
       <c r="F25" t="n">
-        <v>0.0312</v>
+        <v>0.0749</v>
       </c>
     </row>
     <row r="26">
@@ -902,10 +902,10 @@
         <v>13</v>
       </c>
       <c r="E26" t="n">
-        <v>7.1049</v>
+        <v>0.2457</v>
       </c>
       <c r="F26" t="n">
-        <v>0.0003</v>
+        <v>0.0041</v>
       </c>
     </row>
     <row r="27">
@@ -922,10 +922,10 @@
         <v>13</v>
       </c>
       <c r="E27" t="n">
-        <v>3.607</v>
+        <v>0.1909</v>
       </c>
       <c r="F27" t="n">
-        <v>0.0132</v>
+        <v>0.0348</v>
       </c>
     </row>
     <row r="28">
@@ -942,10 +942,10 @@
         <v>14</v>
       </c>
       <c r="E28" t="n">
-        <v>0.7959</v>
+        <v>0.101</v>
       </c>
       <c r="F28" t="n">
-        <v>0.4834</v>
+        <v>0.4751</v>
       </c>
     </row>
     <row r="29">
@@ -962,10 +962,10 @@
         <v>14</v>
       </c>
       <c r="E29" t="n">
-        <v>0.2647</v>
+        <v>0.048</v>
       </c>
       <c r="F29" t="n">
-        <v>0.9615</v>
+        <v>0.9971</v>
       </c>
     </row>
     <row r="30">
@@ -981,8 +981,8 @@
       <c r="D30" t="s">
         <v>15</v>
       </c>
-      <c r="E30" t="e">
-        <v>#NUM!</v>
+      <c r="E30" t="n">
+        <v>0.5183</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
@@ -1001,8 +1001,8 @@
       <c r="D31" t="s">
         <v>15</v>
       </c>
-      <c r="E31" t="e">
-        <v>#NUM!</v>
+      <c r="E31" t="n">
+        <v>0.7467</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
@@ -1022,10 +1022,10 @@
         <v>13</v>
       </c>
       <c r="E32" t="n">
-        <v>0.6784</v>
+        <v>0.0886</v>
       </c>
       <c r="F32" t="n">
-        <v>0.5786</v>
+        <v>0.8166</v>
       </c>
     </row>
     <row r="33">
@@ -1042,10 +1042,10 @@
         <v>13</v>
       </c>
       <c r="E33" t="n">
-        <v>0.2183</v>
+        <v>0.0463</v>
       </c>
       <c r="F33" t="n">
-        <v>0.9874</v>
+        <v>0.8685</v>
       </c>
     </row>
     <row r="34">
@@ -1062,10 +1062,10 @@
         <v>14</v>
       </c>
       <c r="E34" t="n">
-        <v>4.8574</v>
+        <v>0.2387</v>
       </c>
       <c r="F34" t="n">
-        <v>0.0034</v>
+        <v>0.0007</v>
       </c>
     </row>
     <row r="35">
@@ -1082,10 +1082,10 @@
         <v>14</v>
       </c>
       <c r="E35" t="n">
-        <v>2.8787</v>
+        <v>0.187</v>
       </c>
       <c r="F35" t="n">
-        <v>0.0318</v>
+        <v>0.0152</v>
       </c>
     </row>
     <row r="36">
@@ -1101,8 +1101,8 @@
       <c r="D36" t="s">
         <v>15</v>
       </c>
-      <c r="E36" t="e">
-        <v>#NUM!</v>
+      <c r="E36" t="n">
+        <v>0.6527</v>
       </c>
       <c r="F36" t="n">
         <v>0</v>
@@ -1121,8 +1121,8 @@
       <c r="D37" t="s">
         <v>15</v>
       </c>
-      <c r="E37" t="e">
-        <v>#NUM!</v>
+      <c r="E37" t="n">
+        <v>0.8394</v>
       </c>
       <c r="F37" t="n">
         <v>0</v>
@@ -1142,10 +1142,10 @@
         <v>14</v>
       </c>
       <c r="E38" t="n">
-        <v>8.0527</v>
+        <v>0.2043</v>
       </c>
       <c r="F38" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -1162,10 +1162,10 @@
         <v>14</v>
       </c>
       <c r="E39" t="n">
-        <v>4.2524</v>
+        <v>0.1581</v>
       </c>
       <c r="F39" t="n">
-        <v>0.0067</v>
+        <v>0.0069</v>
       </c>
     </row>
     <row r="40">
@@ -1181,8 +1181,8 @@
       <c r="D40" t="s">
         <v>15</v>
       </c>
-      <c r="E40" t="e">
-        <v>#NUM!</v>
+      <c r="E40" t="n">
+        <v>0.7136</v>
       </c>
       <c r="F40" t="n">
         <v>0</v>
@@ -1201,8 +1201,8 @@
       <c r="D41" t="s">
         <v>15</v>
       </c>
-      <c r="E41" t="e">
-        <v>#NUM!</v>
+      <c r="E41" t="n">
+        <v>0.8509</v>
       </c>
       <c r="F41" t="n">
         <v>0</v>
@@ -1221,8 +1221,8 @@
       <c r="D42" t="s">
         <v>15</v>
       </c>
-      <c r="E42" t="e">
-        <v>#NUM!</v>
+      <c r="E42" t="n">
+        <v>0.5094</v>
       </c>
       <c r="F42" t="n">
         <v>0</v>
@@ -1241,8 +1241,8 @@
       <c r="D43" t="s">
         <v>15</v>
       </c>
-      <c r="E43" t="e">
-        <v>#NUM!</v>
+      <c r="E43" t="n">
+        <v>0.7454</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
